--- a/docs/PPG/Metodologia.xlsx
+++ b/docs/PPG/Metodologia.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11130"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10302"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/arthurferreira/Google Drive - arthur_sf/Observatorios/ObservatorioUNISUAM-CR/PPG/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B00C92EE-872D-EC40-B4DA-9A211326DDB3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10E5F6F4-B33B-774D-B114-506FD2674A5C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="880" yWindow="660" windowWidth="27640" windowHeight="16840" xr2:uid="{240D67CA-E89E-3447-B43A-9274A07D4677}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
   <si>
     <t>Formulário</t>
   </si>
@@ -78,6 +78,12 @@
   </si>
   <si>
     <t>https://forms.gle/JoGQAfsmZ6QjYFbA6</t>
+  </si>
+  <si>
+    <t>Atividades Acadêmicas</t>
+  </si>
+  <si>
+    <t>https://forms.gle/Xqp7fPFrSdzKjZEt8</t>
   </si>
 </sst>
 </file>
@@ -449,7 +455,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{13381829-F521-3948-883F-1874EF635CE4}">
-  <dimension ref="A1:B7"/>
+  <dimension ref="A1:B8"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="29.6640625" bestFit="1" customWidth="1"/>
@@ -512,6 +518,14 @@
         <v>5</v>
       </c>
     </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>14</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="B3" r:id="rId1" xr:uid="{119971C0-FBCD-7949-A407-44B46093FD55}"/>
@@ -520,6 +534,7 @@
     <hyperlink ref="B7" r:id="rId4" xr:uid="{50226AE4-0829-FB4C-A97B-4E3F87215804}"/>
     <hyperlink ref="B4" r:id="rId5" xr:uid="{10B895A2-B896-FA4B-8FF6-7693962CADFB}"/>
     <hyperlink ref="B5" r:id="rId6" xr:uid="{4CAC7EB1-1047-C643-836A-D9E1B24A8D7E}"/>
+    <hyperlink ref="B8" r:id="rId7" xr:uid="{F67D38CC-6351-FC44-B8DD-E4C4F25C99B7}"/>
   </hyperlinks>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
